--- a/artfynd/A 55336-2024 artfynd.xlsx
+++ b/artfynd/A 55336-2024 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>120075961</v>
       </c>
       <c r="B2" t="n">
-        <v>56532</v>
+        <v>56566</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/artfynd/A 55336-2024 artfynd.xlsx
+++ b/artfynd/A 55336-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120075961</v>
       </c>
       <c r="B2" t="n">
-        <v>56566</v>
+        <v>56567</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 55336-2024 artfynd.xlsx
+++ b/artfynd/A 55336-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120075961</v>
       </c>
       <c r="B2" t="n">
-        <v>56567</v>
+        <v>56568</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 55336-2024 artfynd.xlsx
+++ b/artfynd/A 55336-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120075961</v>
       </c>
       <c r="B2" t="n">
-        <v>56568</v>
+        <v>56569</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 55336-2024 artfynd.xlsx
+++ b/artfynd/A 55336-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -799,6 +799,124 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>127930939</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56858</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>trafikdödad</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Brandsmo-Ryda, Ryda mader Nittorp  Tranemo, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>407415</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6376311</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Nittorp</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>på vägen mellan Algutstorpasjön och Ryda mader</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jens Ekdal</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jens Ekdal</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55336-2024 artfynd.xlsx
+++ b/artfynd/A 55336-2024 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>127930939</v>
       </c>
       <c r="B3" t="n">
-        <v>56858</v>
+        <v>56861</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 55336-2024 artfynd.xlsx
+++ b/artfynd/A 55336-2024 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>127930939</v>
       </c>
       <c r="B3" t="n">
-        <v>56861</v>
+        <v>56867</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 55336-2024 artfynd.xlsx
+++ b/artfynd/A 55336-2024 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>127930939</v>
       </c>
       <c r="B3" t="n">
-        <v>56867</v>
+        <v>56879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 55336-2024 artfynd.xlsx
+++ b/artfynd/A 55336-2024 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>127930939</v>
       </c>
       <c r="B3" t="n">
-        <v>56879</v>
+        <v>56883</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 55336-2024 artfynd.xlsx
+++ b/artfynd/A 55336-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>120075961</v>
       </c>
       <c r="B2" t="n">
-        <v>56569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +800,7 @@
         <v>127930939</v>
       </c>
       <c r="B3" t="n">
-        <v>56883</v>
+        <v>57144</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 55336-2024 artfynd.xlsx
+++ b/artfynd/A 55336-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -794,6 +799,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120075961</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -912,8 +922,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127930939</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>